--- a/photography_forms/022_holiday_mini_session_rsvp_form--photography_forms.xlsx
+++ b/photography_forms/022_holiday_mini_session_rsvp_form--photography_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1052,7 +1052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -1204,29 +1204,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>special_requests_choices</t>
+          <t>photographer_confirmation_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1238,12 +1238,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1255,29 +1255,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>unable_to_attend</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Unable to attend</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>photographer_confirmation_choices</t>
+          <t>photographer_availability_confirmation_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>unable_to_attend</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Unable to attend</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1289,12 +1289,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1306,29 +1306,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>unable_to_attend</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Unable to attend</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>photographer_availability_confirmation_choices</t>
+          <t>session_date_confirmation_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>unable_to_attend</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Unable to attend</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1340,12 +1340,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1357,29 +1357,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>unable_to_attend</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Unable to attend</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>session_date_confirmation_choices</t>
+          <t>session_time_confirmation_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>unable_to_attend</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Unable to attend</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1391,12 +1391,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1408,29 +1408,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>unable_to_attend</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Unable to attend</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>session_time_confirmation_choices</t>
+          <t>session_location_confirmation_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>unable_to_attend</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Unable to attend</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1442,12 +1442,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1459,29 +1459,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>unable_to_attend</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Unable to attend</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>session_location_confirmation_choices</t>
+          <t>holiday_mini_session_confirmation_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>unable_to_attend</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Unable to attend</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1493,12 +1493,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1510,29 +1510,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>unable_to_attend</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Unable to attend</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>holiday_mini_session_confirmation_choices</t>
+          <t>special_requests_confirmation_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>unable_to_attend</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Unable to attend</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1544,12 +1544,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1561,29 +1561,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>unable_to_attend</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Unable to attend</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>special_requests_confirmation_choices</t>
+          <t>holiday_mini_session_rsvp_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>unable_to_attend</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Unable to attend</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1595,46 +1595,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>holiday_mini_session_rsvp_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>holiday_mini_session_rsvp_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
